--- a/rules/CORE-000338/negative/01/data/unit-test-coreid-CG0457-negative 1.xlsx
+++ b/rules/CORE-000338/negative/01/data/unit-test-coreid-CG0457-negative 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000338\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3D9457-C4D5-4C0D-8AA7-A2F5E8D12A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B0E44C-6363-4169-B1FD-63C30126A8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -643,6 +643,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
